--- a/Inputs/CF_template_parameters_Model.xlsx
+++ b/Inputs/CF_template_parameters_Model.xlsx
@@ -7358,6 +7358,13 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="41d9f072-86bf-4c63-b117-debf50ff4701">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
   </documentManagement>
 </p:properties>
 </file>
@@ -7880,5 +7887,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3F0F0BB-0510-4FEA-B2E4-99B6C15D5F81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D812A3FE-D37C-4E24-8969-990E718A8097}"/>
 </file>